--- a/LvM_Refed_TAGkinetics_portalAAs/LvM_refed_TAGkinetics_hpAAs.xlsx
+++ b/LvM_Refed_TAGkinetics_portalAAs/LvM_refed_TAGkinetics_hpAAs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hui Lab\Desktop\liver_MFA\LvM_Refed_TAGkinetics_portalAAs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boyuan/Desktop/Harvard/Research/Energy Metabolism Atlas/LvM_Refed_TAGkinetics_portalAAs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B57CA1A-731D-43AD-AF59-CD364BB88110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88CBB40-CCA0-DF4B-956B-AFB521FD915A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{5E0D7404-E754-4442-97F6-BA3E5E250F0E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{5E0D7404-E754-4442-97F6-BA3E5E250F0E}"/>
   </bookViews>
   <sheets>
     <sheet name="LvM" sheetId="37" r:id="rId1"/>
@@ -201,9 +201,6 @@
     <t>aKG.Lv -&gt; Gln.Blood</t>
   </si>
   <si>
-    <t>TAG.W -&gt; Glycerol.Blood</t>
-  </si>
-  <si>
     <t>OAA.M + AcCoA.M -&gt; Cit.M</t>
   </si>
   <si>
@@ -317,9 +314,6 @@
     <t>TAG-FA cycle</t>
   </si>
   <si>
-    <t>TAG.W -&gt; Lino.Blood</t>
-  </si>
-  <si>
     <t>Lino.Blood -&gt; sink</t>
   </si>
   <si>
@@ -1993,13 +1987,19 @@
       </rPr>
       <t>-&gt; AcCoA.Lv</t>
     </r>
+  </si>
+  <si>
+    <t>TAGgly.W -&gt; Glycerol.Blood</t>
+  </si>
+  <si>
+    <t>TAGLino.W -&gt; Lino.Blood</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2836,16 +2836,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3255A141-2CCB-574F-8A5D-811344C87C12}">
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" thickBot="1">
+    <row r="1" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2859,25 +2859,25 @@
         <v>12</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="1:5" ht="16.5" thickBot="1">
+    <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24">
         <f>A2+1</f>
         <v>2</v>
@@ -2891,13 +2891,13 @@
       <c r="D3" s="30"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="24">
         <f t="shared" ref="A4:A68" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>16</v>
@@ -2905,13 +2905,13 @@
       <c r="D4" s="30"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:5" ht="16.5" thickBot="1">
+    <row r="5" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>16</v>
@@ -2919,29 +2919,29 @@
       <c r="D5" s="31"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="24">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>3</v>
@@ -2949,13 +2949,13 @@
       <c r="D7" s="55"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>3</v>
@@ -2963,71 +2963,71 @@
       <c r="D8" s="55"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="55"/>
       <c r="E9" s="45" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="24">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="55"/>
       <c r="E10" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="55"/>
       <c r="E11" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C12" s="52" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="55"/>
       <c r="E12" s="53" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3040,16 +3040,16 @@
       </c>
       <c r="D13" s="55"/>
       <c r="E13" s="45" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>6</v>
@@ -3057,13 +3057,13 @@
       <c r="D14" s="55"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="24">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>8</v>
@@ -3071,13 +3071,13 @@
       <c r="D15" s="55"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>9</v>
@@ -3085,13 +3085,13 @@
       <c r="D16" s="55"/>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>9</v>
@@ -3099,13 +3099,13 @@
       <c r="D17" s="55"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="24">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>9</v>
@@ -3113,13 +3113,13 @@
       <c r="D18" s="55"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="24">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>9</v>
@@ -3127,57 +3127,57 @@
       <c r="D19" s="55"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:5" ht="16.5" thickBot="1">
+    <row r="20" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="45" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="24">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="57" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="24">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="58"/>
       <c r="E22" s="45" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3191,13 +3191,13 @@
       <c r="D23" s="58"/>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="24">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>3</v>
@@ -3205,7 +3205,7 @@
       <c r="D24" s="58"/>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="24">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3219,7 +3219,7 @@
       <c r="D25" s="58"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="24">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3233,7 +3233,7 @@
       <c r="D26" s="58"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="24">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3247,7 +3247,7 @@
       <c r="D27" s="58"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="24">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3261,13 +3261,13 @@
       <c r="D28" s="58"/>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="24">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>15</v>
@@ -3275,7 +3275,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="1:5" ht="16.5" thickBot="1">
+    <row r="30" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="24">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3289,7 +3289,7 @@
       <c r="D30" s="59"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="24">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3301,11 +3301,11 @@
         <v>15</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="24">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3319,7 +3319,7 @@
       <c r="D32" s="37"/>
       <c r="E32" s="6"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="24">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -3333,13 +3333,13 @@
       <c r="D33" s="37"/>
       <c r="E33" s="6"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="24">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C34" s="20" t="s">
         <v>3</v>
@@ -3347,13 +3347,13 @@
       <c r="D34" s="37"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="24">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>3</v>
@@ -3361,13 +3361,13 @@
       <c r="D35" s="37"/>
       <c r="E35" s="6"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="24">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>3</v>
@@ -3375,13 +3375,13 @@
       <c r="D36" s="37"/>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:5" ht="16.5" thickBot="1">
+    <row r="37" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>3</v>
@@ -3389,29 +3389,29 @@
       <c r="D37" s="40"/>
       <c r="E37" s="6"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="24">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="60" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E38" s="6"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="24">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>3</v>
@@ -3419,13 +3419,13 @@
       <c r="D39" s="61"/>
       <c r="E39" s="6"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="24">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="42" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>13</v>
@@ -3433,13 +3433,13 @@
       <c r="D40" s="61"/>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="24">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>4</v>
@@ -3447,13 +3447,13 @@
       <c r="D41" s="61"/>
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="24">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>16</v>
@@ -3461,13 +3461,13 @@
       <c r="D42" s="61"/>
       <c r="E42" s="6"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="24">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>16</v>
@@ -3475,13 +3475,13 @@
       <c r="D43" s="61"/>
       <c r="E43" s="6"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="24">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" s="20" t="s">
         <v>5</v>
@@ -3489,13 +3489,13 @@
       <c r="D44" s="61"/>
       <c r="E44" s="6"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="24">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>6</v>
@@ -3503,13 +3503,13 @@
       <c r="D45" s="61"/>
       <c r="E45" s="6"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="24">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>8</v>
@@ -3517,13 +3517,13 @@
       <c r="D46" s="61"/>
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="24">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>9</v>
@@ -3531,13 +3531,13 @@
       <c r="D47" s="61"/>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="24">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>9</v>
@@ -3545,13 +3545,13 @@
       <c r="D48" s="61"/>
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="24">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>9</v>
@@ -3559,13 +3559,13 @@
       <c r="D49" s="61"/>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="24">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>9</v>
@@ -3573,43 +3573,43 @@
       <c r="D50" s="61"/>
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="1:5" ht="16.5" thickBot="1">
+    <row r="51" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="24">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D51" s="62"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="24">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="54" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="24">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>3</v>
@@ -3617,13 +3617,13 @@
       <c r="D53" s="55"/>
       <c r="E53" s="6"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="24">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>3</v>
@@ -3631,13 +3631,13 @@
       <c r="D54" s="55"/>
       <c r="E54" s="6"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="24">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B55" s="46" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C55" s="47" t="s">
         <v>3</v>
@@ -3645,13 +3645,13 @@
       <c r="D55" s="55"/>
       <c r="E55" s="6"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="24">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>16</v>
@@ -3659,13 +3659,13 @@
       <c r="D56" s="55"/>
       <c r="E56" s="6"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="24">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>16</v>
@@ -3673,13 +3673,13 @@
       <c r="D57" s="55"/>
       <c r="E57" s="6"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="24">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>16</v>
@@ -3687,13 +3687,13 @@
       <c r="D58" s="55"/>
       <c r="E58" s="6"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="24">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>16</v>
@@ -3701,13 +3701,13 @@
       <c r="D59" s="55"/>
       <c r="E59" s="6"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="24">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>16</v>
@@ -3715,13 +3715,13 @@
       <c r="D60" s="55"/>
       <c r="E60" s="6"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="24">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>16</v>
@@ -3729,13 +3729,13 @@
       <c r="D61" s="55"/>
       <c r="E61" s="6"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="24">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B62" s="46" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C62" s="47" t="s">
         <v>16</v>
@@ -3743,13 +3743,13 @@
       <c r="D62" s="55"/>
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="24">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>7</v>
@@ -3757,13 +3757,13 @@
       <c r="D63" s="55"/>
       <c r="E63" s="6"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="24">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>7</v>
@@ -3771,13 +3771,13 @@
       <c r="D64" s="55"/>
       <c r="E64" s="6"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="24">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>7</v>
@@ -3785,13 +3785,13 @@
       <c r="D65" s="55"/>
       <c r="E65" s="6"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="24">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>9</v>
@@ -3799,13 +3799,13 @@
       <c r="D66" s="55"/>
       <c r="E66" s="6"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="24">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B67" s="46" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C67" s="47" t="s">
         <v>9</v>
@@ -3813,13 +3813,13 @@
       <c r="D67" s="55"/>
       <c r="E67" s="6"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="24">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>9</v>
@@ -3827,13 +3827,13 @@
       <c r="D68" s="55"/>
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="24">
         <f t="shared" ref="A69:A100" si="1">A68+1</f>
         <v>68</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>9</v>
@@ -3841,13 +3841,13 @@
       <c r="D69" s="55"/>
       <c r="E69" s="6"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="24">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B70" s="46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C70" s="47" t="s">
         <v>9</v>
@@ -3855,13 +3855,13 @@
       <c r="D70" s="55"/>
       <c r="E70" s="6"/>
     </row>
-    <row r="71" spans="1:5" ht="16.5" thickBot="1">
+    <row r="71" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="24">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C71" s="47" t="s">
         <v>9</v>
@@ -3869,7 +3869,7 @@
       <c r="D71" s="56"/>
       <c r="E71" s="6"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="24">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -3881,11 +3881,11 @@
         <v>3</v>
       </c>
       <c r="D72" s="54" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E72" s="6"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="24">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -3899,13 +3899,13 @@
       <c r="D73" s="55"/>
       <c r="E73" s="8"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="24">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>3</v>
@@ -3913,13 +3913,13 @@
       <c r="D74" s="55"/>
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="24">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>3</v>
@@ -3927,13 +3927,13 @@
       <c r="D75" s="55"/>
       <c r="E75" s="6"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="24">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>3</v>
@@ -3941,13 +3941,13 @@
       <c r="D76" s="55"/>
       <c r="E76" s="6"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="24">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>3</v>
@@ -3955,7 +3955,7 @@
       <c r="D77" s="55"/>
       <c r="E77" s="6"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="24">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -3967,11 +3967,11 @@
         <v>7</v>
       </c>
       <c r="D78" s="55" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E78" s="6"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="24">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -3985,7 +3985,7 @@
       <c r="D79" s="55"/>
       <c r="E79" s="6"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="24">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -3999,13 +3999,13 @@
       <c r="D80" s="55"/>
       <c r="E80" s="6"/>
     </row>
-    <row r="81" spans="1:5" ht="16.5" thickBot="1">
+    <row r="81" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="24">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>7</v>
@@ -4013,7 +4013,7 @@
       <c r="D81" s="55"/>
       <c r="E81" s="6"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="24">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -4025,19 +4025,19 @@
         <v>7</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E82" s="45" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="16.5" thickBot="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="24">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>7</v>
@@ -4045,71 +4045,71 @@
       <c r="D83" s="39"/>
       <c r="E83" s="6"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="24">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D84" s="54" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E84" s="6"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="24">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D85" s="55"/>
       <c r="E85" s="6"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="24">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D86" s="55"/>
       <c r="E86" s="6"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="24">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D87" s="55"/>
       <c r="E87" s="6"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="24">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C88" s="25" t="s">
         <v>9</v>
@@ -4117,13 +4117,13 @@
       <c r="D88" s="55"/>
       <c r="E88" s="6"/>
     </row>
-    <row r="89" spans="1:5" ht="16.5" thickBot="1">
+    <row r="89" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="24">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C89" s="25" t="s">
         <v>9</v>
@@ -4131,29 +4131,29 @@
       <c r="D89" s="56"/>
       <c r="E89" s="6"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="24">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C90" s="32" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E90" s="6"/>
     </row>
-    <row r="91" spans="1:5" ht="16.5" thickBot="1">
+    <row r="91" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="24">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C91" s="43" t="s">
         <v>9</v>
@@ -4161,126 +4161,126 @@
       <c r="D91" s="56"/>
       <c r="E91" s="6"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="24">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="24">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D93" s="55"/>
     </row>
-    <row r="94" spans="1:5" ht="16.5" thickBot="1">
+    <row r="94" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="24">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D94" s="56"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="24">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C95" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="54" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="24">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D96" s="55"/>
     </row>
-    <row r="97" spans="1:5" ht="16.5" thickBot="1">
+    <row r="97" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="24">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C97" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D97" s="56"/>
     </row>
-    <row r="98" spans="1:5" ht="16.5" thickBot="1">
+    <row r="98" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="24">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B98" s="49" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C98" s="49" t="s">
         <v>24</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E98" s="6"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="24">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D99" s="54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="24">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C100" s="20" t="s">
         <v>10</v>
@@ -4310,15 +4310,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AE8287-079C-D041-8E27-642CD2612D07}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="3.375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -4332,13 +4332,13 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f>COUNT(LvM!A1:A187) + 1</f>
         <v>100</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -4347,13 +4347,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <f>A2</f>
         <v>100</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
@@ -4362,13 +4362,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <f t="shared" ref="A4:A26" si="0">A3</f>
         <v>100</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -4377,13 +4377,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>3</v>
@@ -4392,13 +4392,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -4407,304 +4407,304 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" thickBot="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="16.5" thickBot="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C16" s="50" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C18" t="s">
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C22" t="s">
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
